--- a/1_Data/Hobbs_2023_PsychMed/Codebook_Hobbs_2023_PsychMed_Exp1_Clean.xlsx
+++ b/1_Data/Hobbs_2023_PsychMed/Codebook_Hobbs_2023_PsychMed_Exp1_Clean.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">Variable_name</t>
   </si>
@@ -162,6 +162,15 @@
   </si>
   <si>
     <t xml:space="preserve">0;1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task type: self-matching = self-referential shape-label matching (names of self/friend/stranger); shape-matching = shape-label matching without a self-referential identity task. The three task conditions of this experiment are carried by the identity columns: Self = Self/Close/Stranger, Valence = happy/neutral/sad, Reward = £9/£3/£1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shape-matching;self-matching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subj_name;Self;Close;Stranger;NonPerson;£9;£3;£1</t>
   </si>
 </sst>
 </file>
@@ -523,10 +532,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -680,7 +689,7 @@
         <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
